--- a/Excel/Visualization.xlsx
+++ b/Excel/Visualization.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ANALYST\AI NIXA\Excel-PowerBI-training-resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A4E62C07-130C-49F8-992D-F4C6BF214DB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{5D8446F8-86B2-4BD8-BE57-B3AE31B7F82A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{F6044C6F-189A-44CE-B37B-70120B822024}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{F6044C6F-189A-44CE-B37B-70120B822024}"/>
   </bookViews>
   <sheets>
     <sheet name="Additional" sheetId="4" r:id="rId1"/>
@@ -5014,15 +5014,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>373380</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>11430</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>68580</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:colOff>335280</xdr:colOff>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>11430</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -6044,17 +6044,8 @@
   <dataFields count="1">
     <dataField name="Sum of Units Sold" fld="4" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="3">
+  <chartFormats count="2">
     <chartFormat chart="3" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -6132,7 +6123,7 @@
   <dataFields count="1">
     <dataField name="Sum of Sales Amount" fld="9" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="2">
+  <chartFormats count="4">
     <chartFormat chart="3" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -6150,6 +6141,30 @@
           </reference>
           <reference field="7" count="1" selected="0">
             <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="7" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="7" count="1" selected="0">
+            <x v="2"/>
           </reference>
         </references>
       </pivotArea>
